--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,26 @@
           <t>types</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>primaryType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>movementStrategy</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hitStrategy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrowSpeed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,33 +459,106 @@
           <t>(list#sep=,),string</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>本期唯一注册投射物类型(SimpleDynamicArrow)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>移动策略标识(TargetEnemyBezierMovement)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>命中策略标识(HitEnemyStrategy)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>箭矢移动速度(px/s,TargetEnemyMovement 默认 200)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>弹道类型列表</t>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>s</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>弹道类型列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
           <t>SimpleDynamicArrow,EagleArrow,FireArrow,HuoFengHuang,LightningChain,ShenBiPunch,PikeSnakeBullet</t>
         </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SimpleDynamicArrow</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TargetEnemyBezierMovement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HitEnemyStrategy</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/projectile.xlsx
+++ b/Configs/GameConfig/Datas/projectile.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R557f4c0dc31a4814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90cbdb97f5414535"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,18 +337,10 @@
       <x:c r="C1" t="str">
         <x:v>types</x:v>
       </x:c>
-      <x:c r="D1" t="str">
-        <x:v>primaryType</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>movementStrategy</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>hitStrategy</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>arrowSpeed</x:v>
-      </x:c>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -360,37 +352,25 @@
       <x:c r="C2" t="str">
         <x:v>(list#sep=,),string</x:v>
       </x:c>
-      <x:c r="D2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3" t="str">
-        <x:v>本期唯一注册投射物类型(SimpleDynamicArrow)</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>移动策略标识(TargetEnemyBezierMovement)</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>命中策略标识(HitEnemyStrategy)</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>箭矢移动速度(px/s,TargetEnemyMovement 默认 200)</x:v>
-      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>占位</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>投射物类型列表</x:v>
+      </x:c>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -399,24 +379,16 @@
       <x:c r="B4"/>
       <x:c r="C4"/>
       <x:c r="D4"/>
-      <x:c r="E4" t="str">
-        <x:v>s</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>s</x:v>
-      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
       <x:c r="G4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>弹道类型列表</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
       <x:c r="D5"/>
       <x:c r="E5"/>
       <x:c r="F5"/>
@@ -430,18 +402,10 @@
       <x:c r="C6" t="str">
         <x:v>SimpleDynamicArrow,EagleArrow,FireArrow,HuoFengHuang,LightningChain,ShenBiPunch,PikeSnakeBullet</x:v>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>SimpleDynamicArrow</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>TargetEnemyBezierMovement</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>HitEnemyStrategy</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>200</x:v>
-      </x:c>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
